--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>85</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>79</v>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2873" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,6 +271,9 @@
     <t>Act[classCode=ACT; moodCode=DEFN]</t>
   </si>
   <si>
+    <t>clinical.general</t>
+  </si>
+  <si>
     <t>ActivityDefinition.id</t>
   </si>
   <si>
@@ -354,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -412,6 +415,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -462,6 +469,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>ActivityDefinition.modifierExtension</t>
   </si>
   <si>
@@ -479,7 +490,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -495,8 +506,8 @@
   </si>
   <si>
     <t>Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
-The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4/resource.html#versions). 
-In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
+The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4B/resource.html#versions). 
+In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4B/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
   </si>
   <si>
     <t>Allows the activity definition to be referenced by a single globally unique identifier.</t>
@@ -579,7 +590,7 @@
     <t>Support human navigation and code generation.</t>
   </si>
   <si>
-    <t xml:space="preserve">inv-0
+    <t xml:space="preserve">cnl-0
 </t>
   </si>
   <si>
@@ -628,7 +639,7 @@
     <t>The lifecycle status of an artifact.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/publication-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/publication-status|4.3.0</t>
   </si>
   <si>
     <t>Definition.status {different ValueSet}</t>
@@ -666,13 +677,16 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group)canonical</t>
   </si>
   <si>
     <t>Type of individual the activity definition is intended for</t>
   </si>
   <si>
-    <t>A code or group definition that describes the intended subject of the activity being defined.</t>
+    <t>A code, group definition, or canonical reference that describes  or identifies the intended subject of the activity being defined.  Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
+  </si>
+  <si>
+    <t>Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
   </si>
   <si>
     <t>Patient</t>
@@ -688,6 +702,9 @@
   </si>
   <si>
     <t>Definition.subject</t>
+  </si>
+  <si>
+    <t>N/A (to add?) { only applies for subject Patient? }</t>
   </si>
   <si>
     <t>ActivityDefinition.date</t>
@@ -990,6 +1007,9 @@
     <t>An individual or organization primarily responsible for internal coherence of the content.</t>
   </si>
   <si>
+    <t>.participation[typeCode=AUT] { not a great match, but there does not appear to be an editor concept in V3 participation }</t>
+  </si>
+  <si>
     <t>ActivityDefinition.editor.id</t>
   </si>
   <si>
@@ -1149,7 +1169,7 @@
     <t>The kind of activity the definition is describing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-resource-types|4.3.0</t>
   </si>
   <si>
     <t>.classCode</t>
@@ -1171,6 +1191,9 @@
     <t>Allows profiles to be used to describe the types of activities that can be performed within a workflow, protocol, or order set.</t>
   </si>
   <si>
+    <t>.templateId</t>
+  </si>
+  <si>
     <t>ActivityDefinition.code</t>
   </si>
   <si>
@@ -1207,7 +1230,10 @@
     <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|4.3.0</t>
+  </si>
+  <si>
+    <t>.moodCode { of the realized Activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.priority</t>
@@ -1222,7 +1248,10 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
+  </si>
+  <si>
+    <t>.priority { of the realized activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.doNotPerform</t>
@@ -1235,6 +1264,9 @@
   </si>
   <si>
     <t>This element is not intended to be used to communicate a decision support response to cancel an order in progress. That should be done with the "remove" type of a PlanDefinition or RequestGroup.</t>
+  </si>
+  <si>
+    <t>.negationInd { of the realized activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.timing[x]</t>
@@ -1295,6 +1327,10 @@
     <t>Indicates who should participate in performing the action described.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
+  </si>
+  <si>
     <t>.participation[typeCode=PFM]</t>
   </si>
   <si>
@@ -1333,7 +1369,7 @@
     <t>The type of participant in the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.3.0</t>
   </si>
   <si>
     <t>.role.classCode</t>
@@ -1351,7 +1387,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
   </si>
   <si>
     <t>.role.code</t>
@@ -1360,7 +1396,7 @@
     <t>ActivityDefinition.product[x]</t>
   </si>
   <si>
-    <t>Reference(Medication|Substance)
+    <t>Reference(Medication|Substance|Ingredient)
 CodeableConcept</t>
   </si>
   <si>
@@ -1526,10 +1562,10 @@
     <t>The path to the element to be set dynamically</t>
   </si>
   <si>
-    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4/fhirpath.html#simple) for full details).</t>
-  </si>
-  <si>
-    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
+    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4B/fhirpath.html#simple) for full details).</t>
+  </si>
+  <si>
+    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4B/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
   </si>
   <si>
     <t>ActivityDefinition.dynamicValue.expression</t>
@@ -1890,7 +1926,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="93.40625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.90625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2134,7 +2170,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>77</v>
@@ -2142,10 +2178,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2156,7 +2192,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -2165,19 +2201,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2227,13 +2263,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2256,10 +2292,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2270,7 +2306,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2279,16 +2315,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2339,19 +2375,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2368,10 +2404,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2382,28 +2418,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2453,19 +2489,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2482,10 +2518,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2496,7 +2532,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2508,16 +2544,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2543,13 +2579,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2567,19 +2603,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2596,21 +2632,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2622,16 +2658,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2681,25 +2717,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2710,14 +2746,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2736,16 +2772,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2795,7 +2831,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2807,13 +2843,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2824,10 +2860,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2850,13 +2886,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2895,17 +2931,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2917,7 +2953,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2934,13 +2970,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2950,10 +2986,10 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>77</v>
@@ -2962,13 +2998,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3019,7 +3055,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3028,10 +3064,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -3048,14 +3084,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3068,25 +3104,25 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3135,7 +3171,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3147,13 +3183,13 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -3164,10 +3200,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3175,10 +3211,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -3187,22 +3223,22 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3251,28 +3287,28 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3280,10 +3316,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3303,22 +3339,22 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3367,7 +3403,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3379,27 +3415,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3410,7 +3446,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3419,19 +3455,19 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3481,28 +3517,28 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3510,10 +3546,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3524,7 +3560,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3533,22 +3569,22 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3597,25 +3633,25 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3626,10 +3662,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3640,7 +3676,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3649,19 +3685,19 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3711,25 +3747,25 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3740,10 +3776,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3754,7 +3790,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3766,13 +3802,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3823,25 +3859,25 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3852,10 +3888,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3863,31 +3899,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3913,13 +3949,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3937,28 +3973,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3966,10 +4002,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3980,7 +4016,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3989,22 +4025,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4053,28 +4089,28 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -4082,10 +4118,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4096,7 +4132,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -4108,21 +4144,23 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q20" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>77</v>
@@ -4143,13 +4181,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -4167,25 +4205,25 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4196,42 +4234,42 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4281,28 +4319,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4310,10 +4348,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4324,7 +4362,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4333,22 +4371,22 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4397,28 +4435,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4426,10 +4464,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4449,19 +4487,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4511,7 +4549,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4523,13 +4561,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4540,10 +4578,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4554,7 +4592,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4563,19 +4601,19 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4625,25 +4663,25 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4654,10 +4692,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4677,22 +4715,22 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4741,7 +4779,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4753,13 +4791,13 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4770,10 +4808,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4793,19 +4831,19 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4831,31 +4869,31 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4867,13 +4905,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4884,10 +4922,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4898,7 +4936,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4910,16 +4948,16 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4969,39 +5007,39 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5012,7 +5050,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5024,13 +5062,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5081,25 +5119,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5110,21 +5148,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5136,17 +5174,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5195,39 +5233,39 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5238,10 +5276,10 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
@@ -5250,16 +5288,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5309,39 +5347,39 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5352,10 +5390,10 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -5364,19 +5402,19 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5425,39 +5463,39 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5468,7 +5506,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5477,22 +5515,22 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5541,39 +5579,39 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5596,17 +5634,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5631,31 +5669,31 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5667,13 +5705,13 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5684,10 +5722,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5710,13 +5748,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5767,7 +5805,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5779,13 +5817,13 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5796,10 +5834,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5813,7 +5851,7 @@
         <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -5822,13 +5860,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5879,7 +5917,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5891,13 +5929,13 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5908,10 +5946,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5922,7 +5960,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5934,13 +5972,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5991,13 +6029,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -6009,7 +6047,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6020,14 +6058,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6046,16 +6084,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6093,19 +6131,19 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6117,13 +6155,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6134,10 +6172,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6145,10 +6183,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6157,19 +6195,19 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6219,19 +6257,19 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6248,10 +6286,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6271,16 +6309,16 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6331,7 +6369,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6343,7 +6381,7 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -6360,10 +6398,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6377,7 +6415,7 @@
         <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>77</v>
@@ -6386,13 +6424,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6443,7 +6481,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6455,13 +6493,13 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6472,10 +6510,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6486,7 +6524,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6498,13 +6536,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6555,13 +6593,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6573,7 +6611,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6584,14 +6622,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6610,16 +6648,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6657,19 +6695,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6681,13 +6719,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6698,10 +6736,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6709,10 +6747,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6721,19 +6759,19 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6783,19 +6821,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6812,10 +6850,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6835,16 +6873,16 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6895,7 +6933,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6907,7 +6945,7 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6924,10 +6962,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6941,7 +6979,7 @@
         <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -6950,13 +6988,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7007,7 +7045,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7019,13 +7057,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7036,10 +7074,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7050,7 +7088,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -7062,13 +7100,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7119,13 +7157,13 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
@@ -7137,7 +7175,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7148,14 +7186,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7174,16 +7212,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7221,19 +7259,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7245,13 +7283,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7262,10 +7300,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7273,10 +7311,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7285,19 +7323,19 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7347,19 +7385,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7376,10 +7414,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7399,16 +7437,16 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7459,7 +7497,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7471,7 +7509,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7488,10 +7526,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7514,19 +7552,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7575,7 +7613,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7587,13 +7625,13 @@
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7604,10 +7642,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7630,13 +7668,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7687,7 +7725,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7699,13 +7737,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7716,10 +7754,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7730,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7739,19 +7777,19 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7777,13 +7815,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7801,25 +7839,25 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7830,10 +7868,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7844,7 +7882,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7856,17 +7894,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7915,25 +7953,25 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7944,10 +7982,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7958,7 +7996,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7967,22 +8005,22 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8007,13 +8045,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8031,25 +8069,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8060,10 +8098,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8074,7 +8112,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8086,13 +8124,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8119,13 +8157,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8143,25 +8181,25 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8172,10 +8210,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8186,7 +8224,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8198,13 +8236,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8231,13 +8269,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8255,25 +8293,25 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8284,10 +8322,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8298,28 +8336,28 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8369,25 +8407,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>403</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8398,10 +8436,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8412,7 +8450,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8424,17 +8462,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8483,25 +8521,25 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8512,21 +8550,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8538,19 +8576,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8599,25 +8637,25 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8628,10 +8666,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8654,13 +8692,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8711,7 +8749,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8723,13 +8761,13 @@
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>422</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8740,10 +8778,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8754,7 +8792,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8766,13 +8804,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8823,13 +8861,13 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8841,7 +8879,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8852,14 +8890,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8878,16 +8916,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8937,7 +8975,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8949,13 +8987,13 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8966,14 +9004,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8986,25 +9024,25 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9053,7 +9091,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9065,13 +9103,13 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9082,10 +9120,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9093,10 +9131,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9108,13 +9146,13 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9141,13 +9179,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9165,25 +9203,25 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9194,10 +9232,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9208,7 +9246,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9220,13 +9258,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9253,13 +9291,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9277,25 +9315,25 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9306,10 +9344,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9320,7 +9358,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9332,13 +9370,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9365,13 +9403,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9389,25 +9427,25 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9418,21 +9456,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9444,13 +9482,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9501,25 +9539,25 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9530,10 +9568,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9556,16 +9594,16 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9615,7 +9653,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9627,13 +9665,13 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9644,10 +9682,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9670,19 +9708,19 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9707,13 +9745,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9731,7 +9769,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9743,13 +9781,13 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9760,10 +9798,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9771,7 +9809,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>79</v>
@@ -9786,17 +9824,17 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9845,7 +9883,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9857,13 +9895,13 @@
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9874,10 +9912,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9900,17 +9938,17 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9959,7 +9997,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9971,13 +10009,13 @@
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9988,10 +10026,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10014,13 +10052,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10071,7 +10109,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10083,13 +10121,13 @@
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -10100,10 +10138,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10114,7 +10152,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10126,16 +10164,16 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10185,25 +10223,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10214,10 +10252,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10240,16 +10278,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10299,7 +10337,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10311,13 +10349,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>97</v>
+        <v>422</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10328,10 +10366,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10342,7 +10380,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10354,13 +10392,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10411,13 +10449,13 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
@@ -10429,7 +10467,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10440,14 +10478,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10466,16 +10504,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10525,7 +10563,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10537,13 +10575,13 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10554,14 +10592,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10574,25 +10612,25 @@
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10641,7 +10679,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10653,13 +10691,13 @@
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10670,10 +10708,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10681,10 +10719,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10696,16 +10734,16 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10755,25 +10793,25 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10784,10 +10822,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10795,10 +10833,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10810,16 +10848,16 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10869,25 +10907,25 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2873" uniqueCount="493">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,9 +271,6 @@
     <t>Act[classCode=ACT; moodCode=DEFN]</t>
   </si>
   <si>
-    <t>clinical.general</t>
-  </si>
-  <si>
     <t>ActivityDefinition.id</t>
   </si>
   <si>
@@ -357,7 +354,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,10 +412,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -469,10 +462,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>ActivityDefinition.modifierExtension</t>
   </si>
   <si>
@@ -490,7 +479,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -506,8 +495,8 @@
   </si>
   <si>
     <t>Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
-The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4B/resource.html#versions). 
-In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4B/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
+The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4/resource.html#versions). 
+In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
   </si>
   <si>
     <t>Allows the activity definition to be referenced by a single globally unique identifier.</t>
@@ -590,7 +579,7 @@
     <t>Support human navigation and code generation.</t>
   </si>
   <si>
-    <t xml:space="preserve">cnl-0
+    <t xml:space="preserve">inv-0
 </t>
   </si>
   <si>
@@ -639,7 +628,7 @@
     <t>The lifecycle status of an artifact.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/publication-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/publication-status|4.0.1</t>
   </si>
   <si>
     <t>Definition.status {different ValueSet}</t>
@@ -677,16 +666,13 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)canonical</t>
+Reference(Group)</t>
   </si>
   <si>
     <t>Type of individual the activity definition is intended for</t>
   </si>
   <si>
-    <t>A code, group definition, or canonical reference that describes  or identifies the intended subject of the activity being defined.  Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
-  </si>
-  <si>
-    <t>Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
+    <t>A code or group definition that describes the intended subject of the activity being defined.</t>
   </si>
   <si>
     <t>Patient</t>
@@ -702,9 +688,6 @@
   </si>
   <si>
     <t>Definition.subject</t>
-  </si>
-  <si>
-    <t>N/A (to add?) { only applies for subject Patient? }</t>
   </si>
   <si>
     <t>ActivityDefinition.date</t>
@@ -1007,9 +990,6 @@
     <t>An individual or organization primarily responsible for internal coherence of the content.</t>
   </si>
   <si>
-    <t>.participation[typeCode=AUT] { not a great match, but there does not appear to be an editor concept in V3 participation }</t>
-  </si>
-  <si>
     <t>ActivityDefinition.editor.id</t>
   </si>
   <si>
@@ -1169,7 +1149,7 @@
     <t>The kind of activity the definition is describing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-resource-types|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/request-resource-types|4.0.1</t>
   </si>
   <si>
     <t>.classCode</t>
@@ -1191,9 +1171,6 @@
     <t>Allows profiles to be used to describe the types of activities that can be performed within a workflow, protocol, or order set.</t>
   </si>
   <si>
-    <t>.templateId</t>
-  </si>
-  <si>
     <t>ActivityDefinition.code</t>
   </si>
   <si>
@@ -1230,10 +1207,7 @@
     <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.3.0</t>
-  </si>
-  <si>
-    <t>.moodCode { of the realized Activity }</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
   </si>
   <si>
     <t>ActivityDefinition.priority</t>
@@ -1248,10 +1222,7 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
-  </si>
-  <si>
-    <t>.priority { of the realized activity }</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
   </si>
   <si>
     <t>ActivityDefinition.doNotPerform</t>
@@ -1264,9 +1235,6 @@
   </si>
   <si>
     <t>This element is not intended to be used to communicate a decision support response to cancel an order in progress. That should be done with the "remove" type of a PlanDefinition or RequestGroup.</t>
-  </si>
-  <si>
-    <t>.negationInd { of the realized activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.timing[x]</t>
@@ -1327,10 +1295,6 @@
     <t>Indicates who should participate in performing the action described.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
     <t>.participation[typeCode=PFM]</t>
   </si>
   <si>
@@ -1369,7 +1333,7 @@
     <t>The type of participant in the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.0.1</t>
   </si>
   <si>
     <t>.role.classCode</t>
@@ -1387,7 +1351,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
   </si>
   <si>
     <t>.role.code</t>
@@ -1396,7 +1360,7 @@
     <t>ActivityDefinition.product[x]</t>
   </si>
   <si>
-    <t>Reference(Medication|Substance|Ingredient)
+    <t>Reference(Medication|Substance)
 CodeableConcept</t>
   </si>
   <si>
@@ -1562,10 +1526,10 @@
     <t>The path to the element to be set dynamically</t>
   </si>
   <si>
-    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4B/fhirpath.html#simple) for full details).</t>
-  </si>
-  <si>
-    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4B/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
+    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4/fhirpath.html#simple) for full details).</t>
+  </si>
+  <si>
+    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
   </si>
   <si>
     <t>ActivityDefinition.dynamicValue.expression</t>
@@ -1926,7 +1890,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="93.40625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.90625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2170,7 +2134,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>77</v>
@@ -2178,10 +2142,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2192,28 +2156,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2263,13 +2227,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2292,10 +2256,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2306,25 +2270,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2375,19 +2339,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2404,10 +2368,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2418,28 +2382,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2489,19 +2453,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2518,10 +2482,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2532,7 +2496,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2544,16 +2508,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2579,43 +2543,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2632,21 +2596,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2658,16 +2622,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2717,25 +2681,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2746,14 +2710,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2772,16 +2736,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2831,7 +2795,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2843,13 +2807,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2860,10 +2824,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2886,13 +2850,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2931,17 +2895,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2953,7 +2917,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2970,13 +2934,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2986,11 +2950,11 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H10" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="I10" t="s" s="2">
         <v>77</v>
       </c>
@@ -2998,13 +2962,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3055,7 +3019,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3064,10 +3028,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -3084,14 +3048,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3104,25 +3068,25 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3171,7 +3135,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3183,13 +3147,13 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -3200,10 +3164,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3211,34 +3175,34 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3287,28 +3251,28 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3316,10 +3280,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3339,22 +3303,22 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3403,7 +3367,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3415,27 +3379,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3446,28 +3410,28 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J14" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3517,28 +3481,28 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3546,10 +3510,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3560,31 +3524,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3633,25 +3597,25 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3662,10 +3626,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3676,28 +3640,28 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3747,25 +3711,25 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3776,10 +3740,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3790,7 +3754,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3802,13 +3766,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3859,25 +3823,25 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3888,10 +3852,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3899,31 +3863,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="J18" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K18" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3949,52 +3913,52 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -4002,10 +3966,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4016,31 +3980,31 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="O19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4089,28 +4053,28 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -4118,10 +4082,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4132,7 +4096,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -4144,86 +4108,84 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="R20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="R20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="AL20" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4234,42 +4196,42 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4319,28 +4281,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4348,10 +4310,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4362,31 +4324,31 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4435,28 +4397,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="AL22" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4464,10 +4426,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4487,19 +4449,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4549,7 +4511,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4561,13 +4523,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4578,10 +4540,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4592,28 +4554,28 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4663,25 +4625,25 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>250</v>
-      </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4692,10 +4654,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4715,22 +4677,22 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4779,7 +4741,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4791,13 +4753,13 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4808,10 +4770,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4831,19 +4793,19 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4869,13 +4831,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4893,7 +4855,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4905,13 +4867,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4922,10 +4884,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4936,7 +4898,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4948,16 +4910,16 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5007,39 +4969,39 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5050,7 +5012,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5062,13 +5024,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5119,25 +5081,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5148,21 +5110,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5174,17 +5136,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5233,39 +5195,39 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AL29" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5276,11 +5238,11 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H30" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5288,16 +5250,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5347,39 +5309,39 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5390,11 +5352,11 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H31" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5402,19 +5364,19 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5463,39 +5425,39 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5506,31 +5468,31 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5579,39 +5541,39 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5634,17 +5596,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5669,13 +5631,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5693,7 +5655,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5705,13 +5667,13 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5722,10 +5684,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5748,13 +5710,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5805,7 +5767,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5817,13 +5779,13 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5834,10 +5796,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5851,7 +5813,7 @@
         <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -5860,13 +5822,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5917,7 +5879,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5929,13 +5891,13 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5946,10 +5908,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5960,7 +5922,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5972,13 +5934,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6029,13 +5991,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -6047,7 +6009,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6058,14 +6020,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6084,16 +6046,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6131,19 +6093,19 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6155,13 +6117,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6172,10 +6134,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6183,31 +6145,31 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G38" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6257,19 +6219,19 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6286,10 +6248,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6309,16 +6271,16 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6369,7 +6331,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6381,7 +6343,7 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -6398,10 +6360,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6415,7 +6377,7 @@
         <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>77</v>
@@ -6424,13 +6386,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6481,7 +6443,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6493,13 +6455,13 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6510,10 +6472,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6524,7 +6486,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6536,13 +6498,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6593,13 +6555,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6611,7 +6573,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6622,14 +6584,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6648,16 +6610,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6695,19 +6657,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6719,13 +6681,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6736,10 +6698,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6747,31 +6709,31 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K43" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6821,19 +6783,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6850,10 +6812,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6873,16 +6835,16 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6933,7 +6895,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6945,7 +6907,7 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6962,10 +6924,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6979,7 +6941,7 @@
         <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -6988,13 +6950,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7045,7 +7007,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7057,13 +7019,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7074,10 +7036,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7088,7 +7050,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -7100,13 +7062,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7157,13 +7119,13 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
@@ -7175,7 +7137,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7186,14 +7148,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7212,16 +7174,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7259,19 +7221,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7283,13 +7245,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7300,10 +7262,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7311,31 +7273,31 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7385,19 +7347,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7414,10 +7376,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7437,16 +7399,16 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7497,7 +7459,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7509,7 +7471,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7526,10 +7488,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7552,19 +7514,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7613,7 +7575,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7625,13 +7587,13 @@
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7642,10 +7604,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7668,13 +7630,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7725,7 +7687,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7737,13 +7699,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7754,10 +7716,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7768,28 +7730,28 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7815,13 +7777,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7839,25 +7801,25 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7868,10 +7830,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7882,7 +7844,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7894,17 +7856,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7953,25 +7915,25 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7982,10 +7944,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7996,31 +7958,31 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="K54" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8045,13 +8007,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8069,25 +8031,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8098,10 +8060,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8112,7 +8074,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8124,13 +8086,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8157,13 +8119,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8181,25 +8143,25 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8210,10 +8172,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8224,7 +8186,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8236,13 +8198,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8269,13 +8231,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8293,25 +8255,25 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8322,10 +8284,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8336,28 +8298,28 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8407,25 +8369,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>403</v>
+        <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8436,10 +8398,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8450,7 +8412,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8462,17 +8424,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8521,25 +8483,25 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8550,21 +8512,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8576,19 +8538,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8637,25 +8599,25 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8666,10 +8628,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8692,13 +8654,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8749,7 +8711,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8761,13 +8723,13 @@
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>422</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8778,10 +8740,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8792,7 +8754,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8804,13 +8766,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8861,13 +8823,13 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8879,7 +8841,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8890,14 +8852,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8916,16 +8878,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8975,7 +8937,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8987,13 +8949,13 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9004,14 +8966,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9024,25 +8986,25 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9091,7 +9053,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9103,13 +9065,13 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9120,10 +9082,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9131,10 +9093,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9146,13 +9108,13 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9179,13 +9141,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9203,25 +9165,25 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9232,10 +9194,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9246,7 +9208,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9258,13 +9220,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9291,13 +9253,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9315,25 +9277,25 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9344,10 +9306,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9358,7 +9320,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9370,13 +9332,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9403,13 +9365,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9427,25 +9389,25 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9456,21 +9418,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9482,13 +9444,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9539,25 +9501,25 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9568,10 +9530,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9594,16 +9556,16 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9653,7 +9615,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9665,13 +9627,13 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9682,10 +9644,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9708,19 +9670,19 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9745,13 +9707,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9769,7 +9731,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9781,13 +9743,13 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9798,10 +9760,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9809,7 +9771,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>79</v>
@@ -9824,17 +9786,17 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9883,7 +9845,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9895,13 +9857,13 @@
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9912,10 +9874,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9938,17 +9900,17 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9997,7 +9959,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10009,13 +9971,13 @@
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -10026,10 +9988,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10052,13 +10014,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10109,7 +10071,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10121,13 +10083,13 @@
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -10138,10 +10100,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10152,7 +10114,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10164,16 +10126,16 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10223,25 +10185,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10252,10 +10214,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10278,16 +10240,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10337,7 +10299,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10349,13 +10311,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>422</v>
+        <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10366,10 +10328,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10380,7 +10342,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10392,13 +10354,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10449,13 +10411,13 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
@@ -10467,7 +10429,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10478,14 +10440,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10504,16 +10466,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10563,7 +10525,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10575,13 +10537,13 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10592,14 +10554,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10612,25 +10574,25 @@
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10679,7 +10641,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10691,13 +10653,13 @@
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10708,10 +10670,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10719,10 +10681,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10734,16 +10696,16 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10793,25 +10755,25 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10822,10 +10784,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10833,10 +10795,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10848,16 +10810,16 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10907,25 +10869,25 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
